--- a/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>ELP</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4509000</v>
+        <v>4304900</v>
       </c>
       <c r="E8" s="3">
-        <v>4931900</v>
+        <v>4394800</v>
       </c>
       <c r="F8" s="3">
-        <v>3831600</v>
+        <v>4806900</v>
       </c>
       <c r="G8" s="3">
-        <v>3263200</v>
+        <v>3734500</v>
       </c>
       <c r="H8" s="3">
-        <v>3071000</v>
+        <v>3180500</v>
       </c>
       <c r="I8" s="3">
-        <v>2883900</v>
+        <v>2993200</v>
       </c>
       <c r="J8" s="3">
+        <v>2810800</v>
+      </c>
+      <c r="K8" s="3">
         <v>2694100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2894000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2742800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1717900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1983300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1929100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3481000</v>
+        <v>3323200</v>
       </c>
       <c r="E9" s="3">
-        <v>3931600</v>
+        <v>3392800</v>
       </c>
       <c r="F9" s="3">
-        <v>2744700</v>
+        <v>3832000</v>
       </c>
       <c r="G9" s="3">
-        <v>2357400</v>
+        <v>2675200</v>
       </c>
       <c r="H9" s="3">
-        <v>2365100</v>
+        <v>2297600</v>
       </c>
       <c r="I9" s="3">
-        <v>2193200</v>
+        <v>2305200</v>
       </c>
       <c r="J9" s="3">
+        <v>2137700</v>
+      </c>
+      <c r="K9" s="3">
         <v>2104400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2284700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2224600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1317000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1527400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1353800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1028000</v>
+        <v>981700</v>
       </c>
       <c r="E10" s="3">
-        <v>1000300</v>
+        <v>1002000</v>
       </c>
       <c r="F10" s="3">
-        <v>1086800</v>
+        <v>975000</v>
       </c>
       <c r="G10" s="3">
-        <v>905800</v>
+        <v>1059300</v>
       </c>
       <c r="H10" s="3">
-        <v>705900</v>
+        <v>882900</v>
       </c>
       <c r="I10" s="3">
-        <v>690600</v>
+        <v>688100</v>
       </c>
       <c r="J10" s="3">
+        <v>673100</v>
+      </c>
+      <c r="K10" s="3">
         <v>589700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>609300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>518200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>456000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>575300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,17 +960,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>374600</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>365200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -971,8 +990,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>17000</v>
+        <v>20800</v>
       </c>
       <c r="E15" s="3">
-        <v>13600</v>
+        <v>16600</v>
       </c>
       <c r="F15" s="3">
         <v>13200</v>
       </c>
       <c r="G15" s="3">
-        <v>11900</v>
+        <v>12900</v>
       </c>
       <c r="H15" s="3">
-        <v>8100</v>
+        <v>11600</v>
       </c>
       <c r="I15" s="3">
-        <v>9400</v>
+        <v>7900</v>
       </c>
       <c r="J15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4117300</v>
+        <v>3564400</v>
       </c>
       <c r="E17" s="3">
-        <v>3812000</v>
+        <v>4013000</v>
       </c>
       <c r="F17" s="3">
-        <v>2957000</v>
+        <v>3715400</v>
       </c>
       <c r="G17" s="3">
-        <v>2584100</v>
+        <v>2882000</v>
       </c>
       <c r="H17" s="3">
-        <v>2578800</v>
+        <v>2518700</v>
       </c>
       <c r="I17" s="3">
-        <v>2442400</v>
+        <v>2513400</v>
       </c>
       <c r="J17" s="3">
+        <v>2380500</v>
+      </c>
+      <c r="K17" s="3">
         <v>2273800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2482200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2402500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1488400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1750000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1591900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>391700</v>
+        <v>740500</v>
       </c>
       <c r="E18" s="3">
-        <v>1119900</v>
+        <v>381800</v>
       </c>
       <c r="F18" s="3">
-        <v>874600</v>
+        <v>1091500</v>
       </c>
       <c r="G18" s="3">
-        <v>679000</v>
+        <v>852400</v>
       </c>
       <c r="H18" s="3">
-        <v>492300</v>
+        <v>661800</v>
       </c>
       <c r="I18" s="3">
-        <v>441500</v>
+        <v>479800</v>
       </c>
       <c r="J18" s="3">
+        <v>430300</v>
+      </c>
+      <c r="K18" s="3">
         <v>420300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>411700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>340300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>229500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>233300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>337200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>107800</v>
+        <v>117100</v>
       </c>
       <c r="E20" s="3">
-        <v>108700</v>
+        <v>105100</v>
       </c>
       <c r="F20" s="3">
-        <v>303100</v>
+        <v>105900</v>
       </c>
       <c r="G20" s="3">
-        <v>268400</v>
+        <v>295400</v>
       </c>
       <c r="H20" s="3">
-        <v>89100</v>
+        <v>261600</v>
       </c>
       <c r="I20" s="3">
-        <v>49300</v>
+        <v>86900</v>
       </c>
       <c r="J20" s="3">
+        <v>48100</v>
+      </c>
+      <c r="K20" s="3">
         <v>69500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>81900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>98000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>96100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>24900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>90800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>767100</v>
+        <v>1135600</v>
       </c>
       <c r="E21" s="3">
-        <v>1451200</v>
+        <v>748600</v>
       </c>
       <c r="F21" s="3">
-        <v>1385400</v>
+        <v>1415200</v>
       </c>
       <c r="G21" s="3">
-        <v>1172500</v>
+        <v>1351000</v>
       </c>
       <c r="H21" s="3">
-        <v>735500</v>
+        <v>1143600</v>
       </c>
       <c r="I21" s="3">
-        <v>641300</v>
+        <v>717400</v>
       </c>
       <c r="J21" s="3">
+        <v>625600</v>
+      </c>
+      <c r="K21" s="3">
         <v>635600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>625100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>564000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>438600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>388100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>563000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>304100</v>
+        <v>358600</v>
       </c>
       <c r="E22" s="3">
-        <v>176000</v>
+        <v>296400</v>
       </c>
       <c r="F22" s="3">
-        <v>124900</v>
+        <v>171500</v>
       </c>
       <c r="G22" s="3">
-        <v>362100</v>
+        <v>121800</v>
       </c>
       <c r="H22" s="3">
-        <v>179200</v>
+        <v>352900</v>
       </c>
       <c r="I22" s="3">
-        <v>204400</v>
+        <v>174600</v>
       </c>
       <c r="J22" s="3">
+        <v>199200</v>
+      </c>
+      <c r="K22" s="3">
         <v>220600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>145500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>72300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>43700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35100</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>195400</v>
+        <v>499000</v>
       </c>
       <c r="E23" s="3">
-        <v>1052600</v>
+        <v>190400</v>
       </c>
       <c r="F23" s="3">
-        <v>1052700</v>
+        <v>1025900</v>
       </c>
       <c r="G23" s="3">
-        <v>585400</v>
+        <v>1026100</v>
       </c>
       <c r="H23" s="3">
-        <v>402200</v>
+        <v>570600</v>
       </c>
       <c r="I23" s="3">
-        <v>286400</v>
+        <v>392000</v>
       </c>
       <c r="J23" s="3">
+        <v>279200</v>
+      </c>
+      <c r="K23" s="3">
         <v>269300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>348100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>366100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>281900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>227100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>392900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-40900</v>
+        <v>71000</v>
       </c>
       <c r="E24" s="3">
-        <v>259000</v>
+        <v>-39900</v>
       </c>
       <c r="F24" s="3">
-        <v>264300</v>
+        <v>252500</v>
       </c>
       <c r="G24" s="3">
-        <v>138900</v>
+        <v>257600</v>
       </c>
       <c r="H24" s="3">
-        <v>105300</v>
+        <v>135400</v>
       </c>
       <c r="I24" s="3">
-        <v>56500</v>
+        <v>102600</v>
       </c>
       <c r="J24" s="3">
+        <v>55100</v>
+      </c>
+      <c r="K24" s="3">
         <v>106900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>103100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>102900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>75800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>57400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>101000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>236300</v>
+        <v>428000</v>
       </c>
       <c r="E26" s="3">
-        <v>793500</v>
+        <v>230300</v>
       </c>
       <c r="F26" s="3">
-        <v>788400</v>
+        <v>773400</v>
       </c>
       <c r="G26" s="3">
-        <v>446500</v>
+        <v>768400</v>
       </c>
       <c r="H26" s="3">
-        <v>296900</v>
+        <v>435200</v>
       </c>
       <c r="I26" s="3">
-        <v>229900</v>
+        <v>289400</v>
       </c>
       <c r="J26" s="3">
+        <v>224100</v>
+      </c>
+      <c r="K26" s="3">
         <v>162400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>245000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>263200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>206100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>169700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>292000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>228700</v>
+        <v>414300</v>
       </c>
       <c r="E27" s="3">
-        <v>773800</v>
+        <v>222900</v>
       </c>
       <c r="F27" s="3">
-        <v>787300</v>
+        <v>754200</v>
       </c>
       <c r="G27" s="3">
-        <v>431500</v>
+        <v>767300</v>
       </c>
       <c r="H27" s="3">
-        <v>289300</v>
+        <v>420500</v>
       </c>
       <c r="I27" s="3">
-        <v>212500</v>
+        <v>282000</v>
       </c>
       <c r="J27" s="3">
+        <v>207200</v>
+      </c>
+      <c r="K27" s="3">
         <v>170300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>230900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>237600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>163600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>287200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,26 +1580,29 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>38400</v>
       </c>
       <c r="E29" s="3">
-        <v>244600</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>15500</v>
+        <v>238400</v>
       </c>
       <c r="G29" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+        <v>15100</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-21700</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
@@ -1556,8 +1616,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-107800</v>
+        <v>-117100</v>
       </c>
       <c r="E32" s="3">
-        <v>-108700</v>
+        <v>-105100</v>
       </c>
       <c r="F32" s="3">
-        <v>-303100</v>
+        <v>-105900</v>
       </c>
       <c r="G32" s="3">
-        <v>-268400</v>
+        <v>-295400</v>
       </c>
       <c r="H32" s="3">
-        <v>-89100</v>
+        <v>-261600</v>
       </c>
       <c r="I32" s="3">
-        <v>-49300</v>
+        <v>-86900</v>
       </c>
       <c r="J32" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-69500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-81900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-98000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-96100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-24900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-90800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>228700</v>
+        <v>452700</v>
       </c>
       <c r="E33" s="3">
-        <v>1018400</v>
+        <v>222900</v>
       </c>
       <c r="F33" s="3">
-        <v>802800</v>
+        <v>992600</v>
       </c>
       <c r="G33" s="3">
-        <v>409200</v>
+        <v>782500</v>
       </c>
       <c r="H33" s="3">
-        <v>289300</v>
+        <v>398800</v>
       </c>
       <c r="I33" s="3">
-        <v>212500</v>
+        <v>282000</v>
       </c>
       <c r="J33" s="3">
+        <v>207200</v>
+      </c>
+      <c r="K33" s="3">
         <v>170300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>230900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>237600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>163600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>287200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>228700</v>
+        <v>452700</v>
       </c>
       <c r="E35" s="3">
-        <v>1018400</v>
+        <v>222900</v>
       </c>
       <c r="F35" s="3">
-        <v>802800</v>
+        <v>992600</v>
       </c>
       <c r="G35" s="3">
-        <v>409200</v>
+        <v>782500</v>
       </c>
       <c r="H35" s="3">
-        <v>289300</v>
+        <v>398800</v>
       </c>
       <c r="I35" s="3">
-        <v>212500</v>
+        <v>282000</v>
       </c>
       <c r="J35" s="3">
+        <v>207200</v>
+      </c>
+      <c r="K35" s="3">
         <v>170300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>230900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>237600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>163600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>287200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>550800</v>
+        <v>1129300</v>
       </c>
       <c r="E41" s="3">
-        <v>714100</v>
+        <v>536800</v>
       </c>
       <c r="F41" s="3">
-        <v>662700</v>
+        <v>696000</v>
       </c>
       <c r="G41" s="3">
-        <v>604900</v>
+        <v>645900</v>
       </c>
       <c r="H41" s="3">
-        <v>400700</v>
+        <v>589600</v>
       </c>
       <c r="I41" s="3">
-        <v>213900</v>
+        <v>390500</v>
       </c>
       <c r="J41" s="3">
+        <v>208500</v>
+      </c>
+      <c r="K41" s="3">
         <v>201900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>286700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>325900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>340800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>520400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>39200</v>
+        <v>4100</v>
       </c>
       <c r="E42" s="3">
-        <v>82200</v>
+        <v>38200</v>
       </c>
       <c r="F42" s="3">
-        <v>36000</v>
+        <v>80100</v>
       </c>
       <c r="G42" s="3">
-        <v>73800</v>
+        <v>35100</v>
       </c>
       <c r="H42" s="3">
-        <v>112300</v>
+        <v>71900</v>
       </c>
       <c r="I42" s="3">
-        <v>35600</v>
+        <v>109400</v>
       </c>
       <c r="J42" s="3">
+        <v>34700</v>
+      </c>
+      <c r="K42" s="3">
         <v>28100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>255000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>210500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>148400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>272400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1275500</v>
+        <v>1274700</v>
       </c>
       <c r="E43" s="3">
-        <v>1452900</v>
+        <v>1243200</v>
       </c>
       <c r="F43" s="3">
-        <v>1352900</v>
+        <v>1416100</v>
       </c>
       <c r="G43" s="3">
-        <v>914000</v>
+        <v>1318600</v>
       </c>
       <c r="H43" s="3">
-        <v>815000</v>
+        <v>890800</v>
       </c>
       <c r="I43" s="3">
-        <v>864600</v>
+        <v>794300</v>
       </c>
       <c r="J43" s="3">
+        <v>842700</v>
+      </c>
+      <c r="K43" s="3">
         <v>658200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>765500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>635600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>446900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>604300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>520200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>40100</v>
+        <v>35000</v>
       </c>
       <c r="E44" s="3">
-        <v>40700</v>
+        <v>39100</v>
       </c>
       <c r="F44" s="3">
-        <v>33500</v>
+        <v>39600</v>
       </c>
       <c r="G44" s="3">
-        <v>26800</v>
+        <v>32600</v>
       </c>
       <c r="H44" s="3">
-        <v>23900</v>
+        <v>26100</v>
       </c>
       <c r="I44" s="3">
-        <v>22700</v>
+        <v>23300</v>
       </c>
       <c r="J44" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K44" s="3">
         <v>26900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>29700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>26100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>58300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>51500</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12400</v>
+        <v>305800</v>
       </c>
       <c r="E45" s="3">
-        <v>11100</v>
+        <v>12100</v>
       </c>
       <c r="F45" s="3">
-        <v>260700</v>
+        <v>10800</v>
       </c>
       <c r="G45" s="3">
-        <v>6900</v>
+        <v>254100</v>
       </c>
       <c r="H45" s="3">
-        <v>21400</v>
+        <v>6800</v>
       </c>
       <c r="I45" s="3">
-        <v>35700</v>
+        <v>20800</v>
       </c>
       <c r="J45" s="3">
+        <v>34800</v>
+      </c>
+      <c r="K45" s="3">
         <v>19300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1918000</v>
+        <v>2748900</v>
       </c>
       <c r="E46" s="3">
-        <v>2301000</v>
+        <v>1869400</v>
       </c>
       <c r="F46" s="3">
-        <v>2345700</v>
+        <v>2242700</v>
       </c>
       <c r="G46" s="3">
-        <v>1626400</v>
+        <v>2286300</v>
       </c>
       <c r="H46" s="3">
-        <v>1373200</v>
+        <v>1585200</v>
       </c>
       <c r="I46" s="3">
-        <v>1172500</v>
+        <v>1338400</v>
       </c>
       <c r="J46" s="3">
+        <v>1142800</v>
+      </c>
+      <c r="K46" s="3">
         <v>871300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1342500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1028300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>875800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1093300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>917800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3596600</v>
+        <v>3499800</v>
       </c>
       <c r="E47" s="3">
-        <v>3513800</v>
+        <v>3505500</v>
       </c>
       <c r="F47" s="3">
-        <v>3270100</v>
+        <v>3424700</v>
       </c>
       <c r="G47" s="3">
-        <v>2187700</v>
+        <v>3187200</v>
       </c>
       <c r="H47" s="3">
-        <v>1953200</v>
+        <v>2132300</v>
       </c>
       <c r="I47" s="3">
-        <v>1748800</v>
+        <v>1903700</v>
       </c>
       <c r="J47" s="3">
+        <v>1704500</v>
+      </c>
+      <c r="K47" s="3">
         <v>1559100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>878300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1448900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1058000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>998600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1013300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2124400</v>
+        <v>2220300</v>
       </c>
       <c r="E48" s="3">
-        <v>2127700</v>
+        <v>2070600</v>
       </c>
       <c r="F48" s="3">
-        <v>1980000</v>
+        <v>2073800</v>
       </c>
       <c r="G48" s="3">
-        <v>2197300</v>
+        <v>1929800</v>
       </c>
       <c r="H48" s="3">
-        <v>2229400</v>
+        <v>2141600</v>
       </c>
       <c r="I48" s="3">
-        <v>2021500</v>
+        <v>2173000</v>
       </c>
       <c r="J48" s="3">
+        <v>1970300</v>
+      </c>
+      <c r="K48" s="3">
         <v>1837400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1683200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1636400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1831200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5514700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3576900</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2113400</v>
+        <v>2238700</v>
       </c>
       <c r="E49" s="3">
-        <v>1895000</v>
+        <v>2059900</v>
       </c>
       <c r="F49" s="3">
-        <v>1424900</v>
+        <v>1847000</v>
       </c>
       <c r="G49" s="3">
-        <v>1302200</v>
+        <v>1388800</v>
       </c>
       <c r="H49" s="3">
-        <v>1239800</v>
+        <v>1269200</v>
       </c>
       <c r="I49" s="3">
-        <v>1326900</v>
+        <v>1208400</v>
       </c>
       <c r="J49" s="3">
+        <v>1293300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1328300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1189900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>428400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>388500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1251000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>860900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>468200</v>
+        <v>479500</v>
       </c>
       <c r="E52" s="3">
-        <v>349000</v>
+        <v>456300</v>
       </c>
       <c r="F52" s="3">
-        <v>599700</v>
+        <v>340100</v>
       </c>
       <c r="G52" s="3">
-        <v>564700</v>
+        <v>584500</v>
       </c>
       <c r="H52" s="3">
-        <v>592700</v>
+        <v>550400</v>
       </c>
       <c r="I52" s="3">
-        <v>603700</v>
+        <v>577700</v>
       </c>
       <c r="J52" s="3">
+        <v>588400</v>
+      </c>
+      <c r="K52" s="3">
         <v>636100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>511300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>506200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>518300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>610900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>551300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10220600</v>
+        <v>11187300</v>
       </c>
       <c r="E54" s="3">
-        <v>10186400</v>
+        <v>9961600</v>
       </c>
       <c r="F54" s="3">
-        <v>9620300</v>
+        <v>9928300</v>
       </c>
       <c r="G54" s="3">
-        <v>7878200</v>
+        <v>9376600</v>
       </c>
       <c r="H54" s="3">
-        <v>7388300</v>
+        <v>7678600</v>
       </c>
       <c r="I54" s="3">
-        <v>6819200</v>
+        <v>7201100</v>
       </c>
       <c r="J54" s="3">
+        <v>6646400</v>
+      </c>
+      <c r="K54" s="3">
         <v>6232300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5605100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5048300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4324800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4952700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4673100</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>429800</v>
+        <v>431800</v>
       </c>
       <c r="E57" s="3">
-        <v>531700</v>
+        <v>418900</v>
       </c>
       <c r="F57" s="3">
-        <v>471200</v>
+        <v>518200</v>
       </c>
       <c r="G57" s="3">
-        <v>346500</v>
+        <v>459200</v>
       </c>
       <c r="H57" s="3">
-        <v>291800</v>
+        <v>337800</v>
       </c>
       <c r="I57" s="3">
-        <v>346200</v>
+        <v>284400</v>
       </c>
       <c r="J57" s="3">
+        <v>337400</v>
+      </c>
+      <c r="K57" s="3">
         <v>258200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>312300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>312800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>204400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>264300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>185400</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>347500</v>
+        <v>391100</v>
       </c>
       <c r="E58" s="3">
-        <v>569900</v>
+        <v>338700</v>
       </c>
       <c r="F58" s="3">
-        <v>542900</v>
+        <v>555500</v>
       </c>
       <c r="G58" s="3">
-        <v>298900</v>
+        <v>529200</v>
       </c>
       <c r="H58" s="3">
-        <v>678200</v>
+        <v>291300</v>
       </c>
       <c r="I58" s="3">
-        <v>497000</v>
+        <v>661000</v>
       </c>
       <c r="J58" s="3">
+        <v>484400</v>
+      </c>
+      <c r="K58" s="3">
         <v>535000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>238700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>256000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>189900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>64000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>28900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>694300</v>
+        <v>1042900</v>
       </c>
       <c r="E59" s="3">
-        <v>539300</v>
+        <v>676700</v>
       </c>
       <c r="F59" s="3">
-        <v>971200</v>
+        <v>525700</v>
       </c>
       <c r="G59" s="3">
-        <v>453800</v>
+        <v>946500</v>
       </c>
       <c r="H59" s="3">
-        <v>406700</v>
+        <v>442300</v>
       </c>
       <c r="I59" s="3">
-        <v>413200</v>
+        <v>396400</v>
       </c>
       <c r="J59" s="3">
+        <v>402800</v>
+      </c>
+      <c r="K59" s="3">
         <v>369800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>376300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>230400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>232200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>423100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>414300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1471600</v>
+        <v>1865800</v>
       </c>
       <c r="E60" s="3">
-        <v>1640900</v>
+        <v>1434300</v>
       </c>
       <c r="F60" s="3">
-        <v>1985200</v>
+        <v>1599400</v>
       </c>
       <c r="G60" s="3">
-        <v>1099200</v>
+        <v>1934900</v>
       </c>
       <c r="H60" s="3">
-        <v>1376700</v>
+        <v>1071400</v>
       </c>
       <c r="I60" s="3">
-        <v>1256400</v>
+        <v>1341800</v>
       </c>
       <c r="J60" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="K60" s="3">
         <v>1163100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>927300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>799200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>626500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>661700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>510500</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2269700</v>
+        <v>2661900</v>
       </c>
       <c r="E61" s="3">
-        <v>1905600</v>
+        <v>2212200</v>
       </c>
       <c r="F61" s="3">
-        <v>1530700</v>
+        <v>1857400</v>
       </c>
       <c r="G61" s="3">
-        <v>2100600</v>
+        <v>1491900</v>
       </c>
       <c r="H61" s="3">
-        <v>1700000</v>
+        <v>2047400</v>
       </c>
       <c r="I61" s="3">
-        <v>1524500</v>
+        <v>1657000</v>
       </c>
       <c r="J61" s="3">
+        <v>1485900</v>
+      </c>
+      <c r="K61" s="3">
         <v>1282100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1264100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>937100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>658200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>697700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>510500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2134000</v>
+        <v>1811100</v>
       </c>
       <c r="E62" s="3">
-        <v>2079900</v>
+        <v>2080000</v>
       </c>
       <c r="F62" s="3">
-        <v>1940300</v>
+        <v>2027200</v>
       </c>
       <c r="G62" s="3">
-        <v>1059700</v>
+        <v>1891100</v>
       </c>
       <c r="H62" s="3">
-        <v>952300</v>
+        <v>1032800</v>
       </c>
       <c r="I62" s="3">
-        <v>848900</v>
+        <v>928200</v>
       </c>
       <c r="J62" s="3">
+        <v>827400</v>
+      </c>
+      <c r="K62" s="3">
         <v>703200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>589700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>615800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>620800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>706600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>655700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5939900</v>
+        <v>6400000</v>
       </c>
       <c r="E66" s="3">
-        <v>5696100</v>
+        <v>5789400</v>
       </c>
       <c r="F66" s="3">
-        <v>5516100</v>
+        <v>5551700</v>
       </c>
       <c r="G66" s="3">
-        <v>4330600</v>
+        <v>5376400</v>
       </c>
       <c r="H66" s="3">
-        <v>4091500</v>
+        <v>4220900</v>
       </c>
       <c r="I66" s="3">
-        <v>3692000</v>
+        <v>3987800</v>
       </c>
       <c r="J66" s="3">
+        <v>3598400</v>
+      </c>
+      <c r="K66" s="3">
         <v>3202600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2846700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2421400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1957400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2127700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1736900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1937900</v>
+        <v>2129700</v>
       </c>
       <c r="E72" s="3">
-        <v>1900500</v>
+        <v>1888800</v>
       </c>
       <c r="F72" s="3">
-        <v>1500800</v>
+        <v>1852300</v>
       </c>
       <c r="G72" s="3">
-        <v>1205100</v>
+        <v>1462700</v>
       </c>
       <c r="H72" s="3">
-        <v>1508800</v>
+        <v>1174600</v>
       </c>
       <c r="I72" s="3">
-        <v>1316500</v>
+        <v>1470500</v>
       </c>
       <c r="J72" s="3">
+        <v>1283100</v>
+      </c>
+      <c r="K72" s="3">
         <v>1197800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1192400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1025100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>846300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>912700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>837200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4280700</v>
+        <v>4787300</v>
       </c>
       <c r="E76" s="3">
-        <v>4490300</v>
+        <v>4172200</v>
       </c>
       <c r="F76" s="3">
-        <v>4104200</v>
+        <v>4376600</v>
       </c>
       <c r="G76" s="3">
-        <v>3547600</v>
+        <v>4000200</v>
       </c>
       <c r="H76" s="3">
-        <v>3296900</v>
+        <v>3457700</v>
       </c>
       <c r="I76" s="3">
-        <v>3127200</v>
+        <v>3213300</v>
       </c>
       <c r="J76" s="3">
+        <v>3048000</v>
+      </c>
+      <c r="K76" s="3">
         <v>3029700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2758400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2626900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2367400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2825000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2936200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>228700</v>
+        <v>452700</v>
       </c>
       <c r="E81" s="3">
-        <v>1018400</v>
+        <v>222900</v>
       </c>
       <c r="F81" s="3">
-        <v>802800</v>
+        <v>992600</v>
       </c>
       <c r="G81" s="3">
-        <v>409200</v>
+        <v>782500</v>
       </c>
       <c r="H81" s="3">
-        <v>289300</v>
+        <v>398800</v>
       </c>
       <c r="I81" s="3">
-        <v>212500</v>
+        <v>282000</v>
       </c>
       <c r="J81" s="3">
+        <v>207200</v>
+      </c>
+      <c r="K81" s="3">
         <v>170300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>230900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>237600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>163600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>287200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>267500</v>
+        <v>277000</v>
       </c>
       <c r="E83" s="3">
-        <v>222600</v>
+        <v>260700</v>
       </c>
       <c r="F83" s="3">
-        <v>207700</v>
+        <v>217000</v>
       </c>
       <c r="G83" s="3">
-        <v>224900</v>
+        <v>202400</v>
       </c>
       <c r="H83" s="3">
-        <v>154100</v>
+        <v>219200</v>
       </c>
       <c r="I83" s="3">
-        <v>150400</v>
+        <v>150200</v>
       </c>
       <c r="J83" s="3">
+        <v>146600</v>
+      </c>
+      <c r="K83" s="3">
         <v>145600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>131000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>124100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>112900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>128400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>137000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>802500</v>
+        <v>705200</v>
       </c>
       <c r="E89" s="3">
-        <v>696400</v>
+        <v>782200</v>
       </c>
       <c r="F89" s="3">
-        <v>810400</v>
+        <v>678800</v>
       </c>
       <c r="G89" s="3">
-        <v>605600</v>
+        <v>789800</v>
       </c>
       <c r="H89" s="3">
-        <v>364200</v>
+        <v>590200</v>
       </c>
       <c r="I89" s="3">
-        <v>203400</v>
+        <v>354900</v>
       </c>
       <c r="J89" s="3">
+        <v>198300</v>
+      </c>
+      <c r="K89" s="3">
         <v>303700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>255700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>215100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>250300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>331400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>285000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-110100</v>
+        <v>-41000</v>
       </c>
       <c r="E91" s="3">
-        <v>-69500</v>
+        <v>-107300</v>
       </c>
       <c r="F91" s="3">
-        <v>-46500</v>
+        <v>-67800</v>
       </c>
       <c r="G91" s="3">
-        <v>-111700</v>
+        <v>-45400</v>
       </c>
       <c r="H91" s="3">
-        <v>-306200</v>
+        <v>-108900</v>
       </c>
       <c r="I91" s="3">
-        <v>-247900</v>
+        <v>-298400</v>
       </c>
       <c r="J91" s="3">
+        <v>-241600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-264100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-145700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-176300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-78600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-204400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-407300</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-570600</v>
+        <v>-628300</v>
       </c>
       <c r="E94" s="3">
-        <v>6600</v>
+        <v>-556200</v>
       </c>
       <c r="F94" s="3">
-        <v>-342900</v>
+        <v>6400</v>
       </c>
       <c r="G94" s="3">
-        <v>-342100</v>
+        <v>-334200</v>
       </c>
       <c r="H94" s="3">
-        <v>-441900</v>
+        <v>-333400</v>
       </c>
       <c r="I94" s="3">
-        <v>-325100</v>
+        <v>-430700</v>
       </c>
       <c r="J94" s="3">
+        <v>-316900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-516400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-377900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-505000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-348800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-426800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-404300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-445800</v>
+        <v>-150400</v>
       </c>
       <c r="E96" s="3">
-        <v>-796700</v>
+        <v>-434500</v>
       </c>
       <c r="F96" s="3">
-        <v>-128800</v>
+        <v>-776500</v>
       </c>
       <c r="G96" s="3">
-        <v>-78200</v>
+        <v>-125500</v>
       </c>
       <c r="H96" s="3">
-        <v>-61800</v>
+        <v>-76200</v>
       </c>
       <c r="I96" s="3">
-        <v>-104100</v>
+        <v>-60300</v>
       </c>
       <c r="J96" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-75900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-59500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-131800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-110700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-52500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-99500</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-395200</v>
+        <v>540400</v>
       </c>
       <c r="E100" s="3">
-        <v>-593100</v>
+        <v>-385200</v>
       </c>
       <c r="F100" s="3">
-        <v>-352700</v>
+        <v>-578100</v>
       </c>
       <c r="G100" s="3">
-        <v>-59200</v>
+        <v>-343700</v>
       </c>
       <c r="H100" s="3">
-        <v>264500</v>
+        <v>-57700</v>
       </c>
       <c r="I100" s="3">
-        <v>133700</v>
+        <v>257800</v>
       </c>
       <c r="J100" s="3">
+        <v>130300</v>
+      </c>
+      <c r="K100" s="3">
         <v>110100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>265600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>92600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>151400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>191300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-65500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4239,49 +4487,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-163400</v>
+        <v>617300</v>
       </c>
       <c r="E102" s="3">
-        <v>109900</v>
+        <v>-159200</v>
       </c>
       <c r="F102" s="3">
-        <v>114800</v>
+        <v>107100</v>
       </c>
       <c r="G102" s="3">
-        <v>204300</v>
+        <v>111900</v>
       </c>
       <c r="H102" s="3">
-        <v>186800</v>
+        <v>199100</v>
       </c>
       <c r="I102" s="3">
-        <v>11900</v>
+        <v>182000</v>
       </c>
       <c r="J102" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-102500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>143400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-197400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>52800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>95900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-184800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4304900</v>
+        <v>3968500</v>
       </c>
       <c r="E8" s="3">
-        <v>4394800</v>
+        <v>4051400</v>
       </c>
       <c r="F8" s="3">
-        <v>4806900</v>
+        <v>4431300</v>
       </c>
       <c r="G8" s="3">
-        <v>3734500</v>
+        <v>3442700</v>
       </c>
       <c r="H8" s="3">
-        <v>3180500</v>
+        <v>2932000</v>
       </c>
       <c r="I8" s="3">
-        <v>2993200</v>
+        <v>2759300</v>
       </c>
       <c r="J8" s="3">
-        <v>2810800</v>
+        <v>2591200</v>
       </c>
       <c r="K8" s="3">
         <v>2694100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3323200</v>
+        <v>3063600</v>
       </c>
       <c r="E9" s="3">
-        <v>3392800</v>
+        <v>3127700</v>
       </c>
       <c r="F9" s="3">
-        <v>3832000</v>
+        <v>3532500</v>
       </c>
       <c r="G9" s="3">
-        <v>2675200</v>
+        <v>2466100</v>
       </c>
       <c r="H9" s="3">
-        <v>2297600</v>
+        <v>2118100</v>
       </c>
       <c r="I9" s="3">
-        <v>2305200</v>
+        <v>2125100</v>
       </c>
       <c r="J9" s="3">
-        <v>2137700</v>
+        <v>1970600</v>
       </c>
       <c r="K9" s="3">
         <v>2104400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>981700</v>
+        <v>905000</v>
       </c>
       <c r="E10" s="3">
-        <v>1002000</v>
+        <v>923700</v>
       </c>
       <c r="F10" s="3">
-        <v>975000</v>
+        <v>898800</v>
       </c>
       <c r="G10" s="3">
-        <v>1059300</v>
+        <v>976500</v>
       </c>
       <c r="H10" s="3">
-        <v>882900</v>
+        <v>813900</v>
       </c>
       <c r="I10" s="3">
-        <v>688100</v>
+        <v>634300</v>
       </c>
       <c r="J10" s="3">
-        <v>673100</v>
+        <v>620600</v>
       </c>
       <c r="K10" s="3">
         <v>589700</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>365200</v>
+        <v>336600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20800</v>
+        <v>19100</v>
       </c>
       <c r="E15" s="3">
-        <v>16600</v>
+        <v>15300</v>
       </c>
       <c r="F15" s="3">
-        <v>13200</v>
+        <v>12200</v>
       </c>
       <c r="G15" s="3">
-        <v>12900</v>
+        <v>11900</v>
       </c>
       <c r="H15" s="3">
-        <v>11600</v>
+        <v>10700</v>
       </c>
       <c r="I15" s="3">
-        <v>7900</v>
+        <v>7300</v>
       </c>
       <c r="J15" s="3">
-        <v>9100</v>
+        <v>8400</v>
       </c>
       <c r="K15" s="3">
         <v>9000</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3564400</v>
+        <v>3285900</v>
       </c>
       <c r="E17" s="3">
-        <v>4013000</v>
+        <v>3699400</v>
       </c>
       <c r="F17" s="3">
-        <v>3715400</v>
+        <v>3425100</v>
       </c>
       <c r="G17" s="3">
-        <v>2882000</v>
+        <v>2656800</v>
       </c>
       <c r="H17" s="3">
-        <v>2518700</v>
+        <v>2321900</v>
       </c>
       <c r="I17" s="3">
-        <v>2513400</v>
+        <v>2317000</v>
       </c>
       <c r="J17" s="3">
-        <v>2380500</v>
+        <v>2194500</v>
       </c>
       <c r="K17" s="3">
         <v>2273800</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>740500</v>
+        <v>682600</v>
       </c>
       <c r="E18" s="3">
-        <v>381800</v>
+        <v>351900</v>
       </c>
       <c r="F18" s="3">
-        <v>1091500</v>
+        <v>1006200</v>
       </c>
       <c r="G18" s="3">
-        <v>852400</v>
+        <v>785800</v>
       </c>
       <c r="H18" s="3">
-        <v>661800</v>
+        <v>610100</v>
       </c>
       <c r="I18" s="3">
-        <v>479800</v>
+        <v>442300</v>
       </c>
       <c r="J18" s="3">
-        <v>430300</v>
+        <v>396700</v>
       </c>
       <c r="K18" s="3">
         <v>420300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>117100</v>
+        <v>107900</v>
       </c>
       <c r="E20" s="3">
-        <v>105100</v>
+        <v>96900</v>
       </c>
       <c r="F20" s="3">
-        <v>105900</v>
+        <v>97600</v>
       </c>
       <c r="G20" s="3">
-        <v>295400</v>
+        <v>272300</v>
       </c>
       <c r="H20" s="3">
-        <v>261600</v>
+        <v>241200</v>
       </c>
       <c r="I20" s="3">
-        <v>86900</v>
+        <v>80100</v>
       </c>
       <c r="J20" s="3">
-        <v>48100</v>
+        <v>44300</v>
       </c>
       <c r="K20" s="3">
         <v>69500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1135600</v>
+        <v>1048100</v>
       </c>
       <c r="E21" s="3">
-        <v>748600</v>
+        <v>691300</v>
       </c>
       <c r="F21" s="3">
-        <v>1415200</v>
+        <v>1305600</v>
       </c>
       <c r="G21" s="3">
-        <v>1351000</v>
+        <v>1246300</v>
       </c>
       <c r="H21" s="3">
-        <v>1143600</v>
+        <v>1055200</v>
       </c>
       <c r="I21" s="3">
-        <v>717400</v>
+        <v>662000</v>
       </c>
       <c r="J21" s="3">
-        <v>625600</v>
+        <v>577300</v>
       </c>
       <c r="K21" s="3">
         <v>635600</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>358600</v>
+        <v>330500</v>
       </c>
       <c r="E22" s="3">
-        <v>296400</v>
+        <v>273300</v>
       </c>
       <c r="F22" s="3">
-        <v>171500</v>
+        <v>158100</v>
       </c>
       <c r="G22" s="3">
-        <v>121800</v>
+        <v>112300</v>
       </c>
       <c r="H22" s="3">
-        <v>352900</v>
+        <v>325300</v>
       </c>
       <c r="I22" s="3">
-        <v>174600</v>
+        <v>161000</v>
       </c>
       <c r="J22" s="3">
-        <v>199200</v>
+        <v>183600</v>
       </c>
       <c r="K22" s="3">
         <v>220600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>499000</v>
+        <v>460000</v>
       </c>
       <c r="E23" s="3">
-        <v>190400</v>
+        <v>175600</v>
       </c>
       <c r="F23" s="3">
-        <v>1025900</v>
+        <v>945700</v>
       </c>
       <c r="G23" s="3">
-        <v>1026100</v>
+        <v>945900</v>
       </c>
       <c r="H23" s="3">
-        <v>570600</v>
+        <v>526000</v>
       </c>
       <c r="I23" s="3">
-        <v>392000</v>
+        <v>361400</v>
       </c>
       <c r="J23" s="3">
-        <v>279200</v>
+        <v>257400</v>
       </c>
       <c r="K23" s="3">
         <v>269300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>71000</v>
+        <v>65400</v>
       </c>
       <c r="E24" s="3">
-        <v>-39900</v>
+        <v>-36800</v>
       </c>
       <c r="F24" s="3">
-        <v>252500</v>
+        <v>232700</v>
       </c>
       <c r="G24" s="3">
-        <v>257600</v>
+        <v>237500</v>
       </c>
       <c r="H24" s="3">
-        <v>135400</v>
+        <v>124800</v>
       </c>
       <c r="I24" s="3">
-        <v>102600</v>
+        <v>94600</v>
       </c>
       <c r="J24" s="3">
-        <v>55100</v>
+        <v>50800</v>
       </c>
       <c r="K24" s="3">
         <v>106900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>428000</v>
+        <v>394600</v>
       </c>
       <c r="E26" s="3">
-        <v>230300</v>
+        <v>212300</v>
       </c>
       <c r="F26" s="3">
-        <v>773400</v>
+        <v>713000</v>
       </c>
       <c r="G26" s="3">
-        <v>768400</v>
+        <v>708400</v>
       </c>
       <c r="H26" s="3">
-        <v>435200</v>
+        <v>401200</v>
       </c>
       <c r="I26" s="3">
-        <v>289400</v>
+        <v>266800</v>
       </c>
       <c r="J26" s="3">
-        <v>224100</v>
+        <v>206600</v>
       </c>
       <c r="K26" s="3">
         <v>162400</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>414300</v>
+        <v>382000</v>
       </c>
       <c r="E27" s="3">
-        <v>222900</v>
+        <v>205500</v>
       </c>
       <c r="F27" s="3">
-        <v>754200</v>
+        <v>695300</v>
       </c>
       <c r="G27" s="3">
-        <v>767300</v>
+        <v>707400</v>
       </c>
       <c r="H27" s="3">
-        <v>420500</v>
+        <v>387700</v>
       </c>
       <c r="I27" s="3">
-        <v>282000</v>
+        <v>260000</v>
       </c>
       <c r="J27" s="3">
-        <v>207200</v>
+        <v>191000</v>
       </c>
       <c r="K27" s="3">
         <v>170300</v>
@@ -1590,19 +1590,19 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>38400</v>
+        <v>35400</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>238400</v>
+        <v>219800</v>
       </c>
       <c r="G29" s="3">
-        <v>15100</v>
+        <v>14000</v>
       </c>
       <c r="H29" s="3">
-        <v>-21700</v>
+        <v>-20000</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-117100</v>
+        <v>-107900</v>
       </c>
       <c r="E32" s="3">
-        <v>-105100</v>
+        <v>-96900</v>
       </c>
       <c r="F32" s="3">
-        <v>-105900</v>
+        <v>-97600</v>
       </c>
       <c r="G32" s="3">
-        <v>-295400</v>
+        <v>-272300</v>
       </c>
       <c r="H32" s="3">
-        <v>-261600</v>
+        <v>-241200</v>
       </c>
       <c r="I32" s="3">
-        <v>-86900</v>
+        <v>-80100</v>
       </c>
       <c r="J32" s="3">
-        <v>-48100</v>
+        <v>-44300</v>
       </c>
       <c r="K32" s="3">
         <v>-69500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>452700</v>
+        <v>417300</v>
       </c>
       <c r="E33" s="3">
-        <v>222900</v>
+        <v>205500</v>
       </c>
       <c r="F33" s="3">
-        <v>992600</v>
+        <v>915000</v>
       </c>
       <c r="G33" s="3">
-        <v>782500</v>
+        <v>721300</v>
       </c>
       <c r="H33" s="3">
-        <v>398800</v>
+        <v>367700</v>
       </c>
       <c r="I33" s="3">
-        <v>282000</v>
+        <v>260000</v>
       </c>
       <c r="J33" s="3">
-        <v>207200</v>
+        <v>191000</v>
       </c>
       <c r="K33" s="3">
         <v>170300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>452700</v>
+        <v>417300</v>
       </c>
       <c r="E35" s="3">
-        <v>222900</v>
+        <v>205500</v>
       </c>
       <c r="F35" s="3">
-        <v>992600</v>
+        <v>915000</v>
       </c>
       <c r="G35" s="3">
-        <v>782500</v>
+        <v>721300</v>
       </c>
       <c r="H35" s="3">
-        <v>398800</v>
+        <v>367700</v>
       </c>
       <c r="I35" s="3">
-        <v>282000</v>
+        <v>260000</v>
       </c>
       <c r="J35" s="3">
-        <v>207200</v>
+        <v>191000</v>
       </c>
       <c r="K35" s="3">
         <v>170300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1129300</v>
+        <v>1041100</v>
       </c>
       <c r="E41" s="3">
-        <v>536800</v>
+        <v>494900</v>
       </c>
       <c r="F41" s="3">
-        <v>696000</v>
+        <v>641600</v>
       </c>
       <c r="G41" s="3">
-        <v>645900</v>
+        <v>595400</v>
       </c>
       <c r="H41" s="3">
-        <v>589600</v>
+        <v>543500</v>
       </c>
       <c r="I41" s="3">
-        <v>390500</v>
+        <v>360000</v>
       </c>
       <c r="J41" s="3">
-        <v>208500</v>
+        <v>192200</v>
       </c>
       <c r="K41" s="3">
         <v>201900</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="E42" s="3">
-        <v>38200</v>
+        <v>35300</v>
       </c>
       <c r="F42" s="3">
-        <v>80100</v>
+        <v>73900</v>
       </c>
       <c r="G42" s="3">
-        <v>35100</v>
+        <v>32300</v>
       </c>
       <c r="H42" s="3">
-        <v>71900</v>
+        <v>66300</v>
       </c>
       <c r="I42" s="3">
-        <v>109400</v>
+        <v>100900</v>
       </c>
       <c r="J42" s="3">
-        <v>34700</v>
+        <v>32000</v>
       </c>
       <c r="K42" s="3">
         <v>28100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1274700</v>
+        <v>1175100</v>
       </c>
       <c r="E43" s="3">
-        <v>1243200</v>
+        <v>1146100</v>
       </c>
       <c r="F43" s="3">
-        <v>1416100</v>
+        <v>1305400</v>
       </c>
       <c r="G43" s="3">
-        <v>1318600</v>
+        <v>1215600</v>
       </c>
       <c r="H43" s="3">
-        <v>890800</v>
+        <v>821200</v>
       </c>
       <c r="I43" s="3">
-        <v>794300</v>
+        <v>732200</v>
       </c>
       <c r="J43" s="3">
-        <v>842700</v>
+        <v>776900</v>
       </c>
       <c r="K43" s="3">
         <v>658200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>35000</v>
+        <v>32300</v>
       </c>
       <c r="E44" s="3">
-        <v>39100</v>
+        <v>36000</v>
       </c>
       <c r="F44" s="3">
-        <v>39600</v>
+        <v>36500</v>
       </c>
       <c r="G44" s="3">
-        <v>32600</v>
+        <v>30100</v>
       </c>
       <c r="H44" s="3">
-        <v>26100</v>
+        <v>24100</v>
       </c>
       <c r="I44" s="3">
-        <v>23300</v>
+        <v>21500</v>
       </c>
       <c r="J44" s="3">
-        <v>22200</v>
+        <v>20400</v>
       </c>
       <c r="K44" s="3">
         <v>26900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>305800</v>
+        <v>281900</v>
       </c>
       <c r="E45" s="3">
-        <v>12100</v>
+        <v>11100</v>
       </c>
       <c r="F45" s="3">
-        <v>10800</v>
+        <v>9900</v>
       </c>
       <c r="G45" s="3">
-        <v>254100</v>
+        <v>234200</v>
       </c>
       <c r="H45" s="3">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="I45" s="3">
-        <v>20800</v>
+        <v>19200</v>
       </c>
       <c r="J45" s="3">
-        <v>34800</v>
+        <v>32000</v>
       </c>
       <c r="K45" s="3">
         <v>19300</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2748900</v>
+        <v>2534100</v>
       </c>
       <c r="E46" s="3">
-        <v>1869400</v>
+        <v>1723300</v>
       </c>
       <c r="F46" s="3">
-        <v>2242700</v>
+        <v>2067400</v>
       </c>
       <c r="G46" s="3">
-        <v>2286300</v>
+        <v>2107600</v>
       </c>
       <c r="H46" s="3">
-        <v>1585200</v>
+        <v>1461300</v>
       </c>
       <c r="I46" s="3">
-        <v>1338400</v>
+        <v>1233800</v>
       </c>
       <c r="J46" s="3">
-        <v>1142800</v>
+        <v>1053500</v>
       </c>
       <c r="K46" s="3">
         <v>871300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3499800</v>
+        <v>3226400</v>
       </c>
       <c r="E47" s="3">
-        <v>3505500</v>
+        <v>3231600</v>
       </c>
       <c r="F47" s="3">
-        <v>3424700</v>
+        <v>3157100</v>
       </c>
       <c r="G47" s="3">
-        <v>3187200</v>
+        <v>2938200</v>
       </c>
       <c r="H47" s="3">
-        <v>2132300</v>
+        <v>1965600</v>
       </c>
       <c r="I47" s="3">
-        <v>1903700</v>
+        <v>1755000</v>
       </c>
       <c r="J47" s="3">
-        <v>1704500</v>
+        <v>1571300</v>
       </c>
       <c r="K47" s="3">
         <v>1559100</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2220300</v>
+        <v>2046900</v>
       </c>
       <c r="E48" s="3">
-        <v>2070600</v>
+        <v>1908800</v>
       </c>
       <c r="F48" s="3">
-        <v>2073800</v>
+        <v>1911700</v>
       </c>
       <c r="G48" s="3">
-        <v>1929800</v>
+        <v>1779000</v>
       </c>
       <c r="H48" s="3">
-        <v>2141600</v>
+        <v>1974300</v>
       </c>
       <c r="I48" s="3">
-        <v>2173000</v>
+        <v>2003200</v>
       </c>
       <c r="J48" s="3">
-        <v>1970300</v>
+        <v>1816300</v>
       </c>
       <c r="K48" s="3">
         <v>1837400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2238700</v>
+        <v>2063800</v>
       </c>
       <c r="E49" s="3">
-        <v>2059900</v>
+        <v>1898900</v>
       </c>
       <c r="F49" s="3">
-        <v>1847000</v>
+        <v>1702700</v>
       </c>
       <c r="G49" s="3">
-        <v>1388800</v>
+        <v>1280300</v>
       </c>
       <c r="H49" s="3">
-        <v>1269200</v>
+        <v>1170000</v>
       </c>
       <c r="I49" s="3">
-        <v>1208400</v>
+        <v>1113900</v>
       </c>
       <c r="J49" s="3">
-        <v>1293300</v>
+        <v>1192200</v>
       </c>
       <c r="K49" s="3">
         <v>1328300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>479500</v>
+        <v>442000</v>
       </c>
       <c r="E52" s="3">
-        <v>456300</v>
+        <v>420700</v>
       </c>
       <c r="F52" s="3">
-        <v>340100</v>
+        <v>313600</v>
       </c>
       <c r="G52" s="3">
-        <v>584500</v>
+        <v>538800</v>
       </c>
       <c r="H52" s="3">
-        <v>550400</v>
+        <v>507400</v>
       </c>
       <c r="I52" s="3">
-        <v>577700</v>
+        <v>532500</v>
       </c>
       <c r="J52" s="3">
-        <v>588400</v>
+        <v>542400</v>
       </c>
       <c r="K52" s="3">
         <v>636100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11187300</v>
+        <v>10313100</v>
       </c>
       <c r="E54" s="3">
-        <v>9961600</v>
+        <v>9183300</v>
       </c>
       <c r="F54" s="3">
-        <v>9928300</v>
+        <v>9152600</v>
       </c>
       <c r="G54" s="3">
-        <v>9376600</v>
+        <v>8643900</v>
       </c>
       <c r="H54" s="3">
-        <v>7678600</v>
+        <v>7078600</v>
       </c>
       <c r="I54" s="3">
-        <v>7201100</v>
+        <v>6638400</v>
       </c>
       <c r="J54" s="3">
-        <v>6646400</v>
+        <v>6127100</v>
       </c>
       <c r="K54" s="3">
         <v>6232300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>431800</v>
+        <v>398100</v>
       </c>
       <c r="E57" s="3">
-        <v>418900</v>
+        <v>386200</v>
       </c>
       <c r="F57" s="3">
-        <v>518200</v>
+        <v>477700</v>
       </c>
       <c r="G57" s="3">
-        <v>459200</v>
+        <v>423300</v>
       </c>
       <c r="H57" s="3">
-        <v>337800</v>
+        <v>311400</v>
       </c>
       <c r="I57" s="3">
-        <v>284400</v>
+        <v>262200</v>
       </c>
       <c r="J57" s="3">
-        <v>337400</v>
+        <v>311100</v>
       </c>
       <c r="K57" s="3">
         <v>258200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>391100</v>
+        <v>360500</v>
       </c>
       <c r="E58" s="3">
-        <v>338700</v>
+        <v>312300</v>
       </c>
       <c r="F58" s="3">
-        <v>555500</v>
+        <v>512100</v>
       </c>
       <c r="G58" s="3">
-        <v>529200</v>
+        <v>487800</v>
       </c>
       <c r="H58" s="3">
-        <v>291300</v>
+        <v>268500</v>
       </c>
       <c r="I58" s="3">
-        <v>661000</v>
+        <v>609300</v>
       </c>
       <c r="J58" s="3">
-        <v>484400</v>
+        <v>446500</v>
       </c>
       <c r="K58" s="3">
         <v>535000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1042900</v>
+        <v>961400</v>
       </c>
       <c r="E59" s="3">
-        <v>676700</v>
+        <v>623800</v>
       </c>
       <c r="F59" s="3">
-        <v>525700</v>
+        <v>484600</v>
       </c>
       <c r="G59" s="3">
-        <v>946500</v>
+        <v>872600</v>
       </c>
       <c r="H59" s="3">
-        <v>442300</v>
+        <v>407800</v>
       </c>
       <c r="I59" s="3">
-        <v>396400</v>
+        <v>365400</v>
       </c>
       <c r="J59" s="3">
-        <v>402800</v>
+        <v>371300</v>
       </c>
       <c r="K59" s="3">
         <v>369800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1865800</v>
+        <v>1720000</v>
       </c>
       <c r="E60" s="3">
-        <v>1434300</v>
+        <v>1322300</v>
       </c>
       <c r="F60" s="3">
-        <v>1599400</v>
+        <v>1474400</v>
       </c>
       <c r="G60" s="3">
-        <v>1934900</v>
+        <v>1783700</v>
       </c>
       <c r="H60" s="3">
-        <v>1071400</v>
+        <v>987700</v>
       </c>
       <c r="I60" s="3">
-        <v>1341800</v>
+        <v>1237000</v>
       </c>
       <c r="J60" s="3">
-        <v>1224500</v>
+        <v>1128900</v>
       </c>
       <c r="K60" s="3">
         <v>1163100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2661900</v>
+        <v>2453900</v>
       </c>
       <c r="E61" s="3">
-        <v>2212200</v>
+        <v>2039400</v>
       </c>
       <c r="F61" s="3">
-        <v>1857400</v>
+        <v>1712200</v>
       </c>
       <c r="G61" s="3">
-        <v>1491900</v>
+        <v>1375400</v>
       </c>
       <c r="H61" s="3">
-        <v>2047400</v>
+        <v>1887400</v>
       </c>
       <c r="I61" s="3">
-        <v>1657000</v>
+        <v>1527500</v>
       </c>
       <c r="J61" s="3">
-        <v>1485900</v>
+        <v>1369800</v>
       </c>
       <c r="K61" s="3">
         <v>1282100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1811100</v>
+        <v>1669600</v>
       </c>
       <c r="E62" s="3">
-        <v>2080000</v>
+        <v>1917400</v>
       </c>
       <c r="F62" s="3">
-        <v>2027200</v>
+        <v>1868800</v>
       </c>
       <c r="G62" s="3">
-        <v>1891100</v>
+        <v>1743300</v>
       </c>
       <c r="H62" s="3">
-        <v>1032800</v>
+        <v>952100</v>
       </c>
       <c r="I62" s="3">
-        <v>928200</v>
+        <v>855700</v>
       </c>
       <c r="J62" s="3">
-        <v>827400</v>
+        <v>762700</v>
       </c>
       <c r="K62" s="3">
         <v>703200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6400000</v>
+        <v>5899900</v>
       </c>
       <c r="E66" s="3">
-        <v>5789400</v>
+        <v>5337000</v>
       </c>
       <c r="F66" s="3">
-        <v>5551700</v>
+        <v>5117900</v>
       </c>
       <c r="G66" s="3">
-        <v>5376400</v>
+        <v>4956300</v>
       </c>
       <c r="H66" s="3">
-        <v>4220900</v>
+        <v>3891100</v>
       </c>
       <c r="I66" s="3">
-        <v>3987800</v>
+        <v>3676200</v>
       </c>
       <c r="J66" s="3">
-        <v>3598400</v>
+        <v>3317300</v>
       </c>
       <c r="K66" s="3">
         <v>3202600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2129700</v>
+        <v>1963300</v>
       </c>
       <c r="E72" s="3">
-        <v>1888800</v>
+        <v>1741200</v>
       </c>
       <c r="F72" s="3">
-        <v>1852300</v>
+        <v>1707600</v>
       </c>
       <c r="G72" s="3">
-        <v>1462700</v>
+        <v>1348400</v>
       </c>
       <c r="H72" s="3">
-        <v>1174600</v>
+        <v>1082800</v>
       </c>
       <c r="I72" s="3">
-        <v>1470500</v>
+        <v>1355600</v>
       </c>
       <c r="J72" s="3">
-        <v>1283100</v>
+        <v>1182900</v>
       </c>
       <c r="K72" s="3">
         <v>1197800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4787300</v>
+        <v>4413200</v>
       </c>
       <c r="E76" s="3">
-        <v>4172200</v>
+        <v>3846200</v>
       </c>
       <c r="F76" s="3">
-        <v>4376600</v>
+        <v>4034600</v>
       </c>
       <c r="G76" s="3">
-        <v>4000200</v>
+        <v>3687600</v>
       </c>
       <c r="H76" s="3">
-        <v>3457700</v>
+        <v>3187600</v>
       </c>
       <c r="I76" s="3">
-        <v>3213300</v>
+        <v>2962200</v>
       </c>
       <c r="J76" s="3">
-        <v>3048000</v>
+        <v>2809800</v>
       </c>
       <c r="K76" s="3">
         <v>3029700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>452700</v>
+        <v>417300</v>
       </c>
       <c r="E81" s="3">
-        <v>222900</v>
+        <v>205500</v>
       </c>
       <c r="F81" s="3">
-        <v>992600</v>
+        <v>915000</v>
       </c>
       <c r="G81" s="3">
-        <v>782500</v>
+        <v>721300</v>
       </c>
       <c r="H81" s="3">
-        <v>398800</v>
+        <v>367700</v>
       </c>
       <c r="I81" s="3">
-        <v>282000</v>
+        <v>260000</v>
       </c>
       <c r="J81" s="3">
-        <v>207200</v>
+        <v>191000</v>
       </c>
       <c r="K81" s="3">
         <v>170300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>277000</v>
+        <v>255300</v>
       </c>
       <c r="E83" s="3">
-        <v>260700</v>
+        <v>240400</v>
       </c>
       <c r="F83" s="3">
-        <v>217000</v>
+        <v>200000</v>
       </c>
       <c r="G83" s="3">
-        <v>202400</v>
+        <v>186600</v>
       </c>
       <c r="H83" s="3">
-        <v>219200</v>
+        <v>202100</v>
       </c>
       <c r="I83" s="3">
-        <v>150200</v>
+        <v>138400</v>
       </c>
       <c r="J83" s="3">
-        <v>146600</v>
+        <v>135200</v>
       </c>
       <c r="K83" s="3">
         <v>145600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>705200</v>
+        <v>650100</v>
       </c>
       <c r="E89" s="3">
-        <v>782200</v>
+        <v>721100</v>
       </c>
       <c r="F89" s="3">
-        <v>678800</v>
+        <v>625800</v>
       </c>
       <c r="G89" s="3">
-        <v>789800</v>
+        <v>728100</v>
       </c>
       <c r="H89" s="3">
-        <v>590200</v>
+        <v>544100</v>
       </c>
       <c r="I89" s="3">
-        <v>354900</v>
+        <v>327200</v>
       </c>
       <c r="J89" s="3">
-        <v>198300</v>
+        <v>182800</v>
       </c>
       <c r="K89" s="3">
         <v>303700</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-41000</v>
+        <v>-37800</v>
       </c>
       <c r="E91" s="3">
-        <v>-107300</v>
+        <v>-98900</v>
       </c>
       <c r="F91" s="3">
-        <v>-67800</v>
+        <v>-62500</v>
       </c>
       <c r="G91" s="3">
-        <v>-45400</v>
+        <v>-41800</v>
       </c>
       <c r="H91" s="3">
-        <v>-108900</v>
+        <v>-100300</v>
       </c>
       <c r="I91" s="3">
-        <v>-298400</v>
+        <v>-275100</v>
       </c>
       <c r="J91" s="3">
-        <v>-241600</v>
+        <v>-222700</v>
       </c>
       <c r="K91" s="3">
         <v>-264100</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-628300</v>
+        <v>-579200</v>
       </c>
       <c r="E94" s="3">
-        <v>-556200</v>
+        <v>-512700</v>
       </c>
       <c r="F94" s="3">
-        <v>6400</v>
+        <v>5900</v>
       </c>
       <c r="G94" s="3">
-        <v>-334200</v>
+        <v>-308100</v>
       </c>
       <c r="H94" s="3">
-        <v>-333400</v>
+        <v>-307400</v>
       </c>
       <c r="I94" s="3">
-        <v>-430700</v>
+        <v>-397100</v>
       </c>
       <c r="J94" s="3">
-        <v>-316900</v>
+        <v>-292100</v>
       </c>
       <c r="K94" s="3">
         <v>-516400</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-150400</v>
+        <v>-138600</v>
       </c>
       <c r="E96" s="3">
-        <v>-434500</v>
+        <v>-400500</v>
       </c>
       <c r="F96" s="3">
-        <v>-776500</v>
+        <v>-715800</v>
       </c>
       <c r="G96" s="3">
-        <v>-125500</v>
+        <v>-115700</v>
       </c>
       <c r="H96" s="3">
-        <v>-76200</v>
+        <v>-70300</v>
       </c>
       <c r="I96" s="3">
-        <v>-60300</v>
+        <v>-55600</v>
       </c>
       <c r="J96" s="3">
-        <v>-101500</v>
+        <v>-93600</v>
       </c>
       <c r="K96" s="3">
         <v>-75900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>540400</v>
+        <v>498200</v>
       </c>
       <c r="E100" s="3">
-        <v>-385200</v>
+        <v>-355100</v>
       </c>
       <c r="F100" s="3">
-        <v>-578100</v>
+        <v>-532900</v>
       </c>
       <c r="G100" s="3">
-        <v>-343700</v>
+        <v>-316900</v>
       </c>
       <c r="H100" s="3">
-        <v>-57700</v>
+        <v>-53200</v>
       </c>
       <c r="I100" s="3">
-        <v>257800</v>
+        <v>237700</v>
       </c>
       <c r="J100" s="3">
-        <v>130300</v>
+        <v>120100</v>
       </c>
       <c r="K100" s="3">
         <v>110100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>617300</v>
+        <v>569100</v>
       </c>
       <c r="E102" s="3">
-        <v>-159200</v>
+        <v>-146800</v>
       </c>
       <c r="F102" s="3">
-        <v>107100</v>
+        <v>98700</v>
       </c>
       <c r="G102" s="3">
-        <v>111900</v>
+        <v>103100</v>
       </c>
       <c r="H102" s="3">
-        <v>199100</v>
+        <v>183500</v>
       </c>
       <c r="I102" s="3">
-        <v>182000</v>
+        <v>167800</v>
       </c>
       <c r="J102" s="3">
-        <v>11600</v>
+        <v>10700</v>
       </c>
       <c r="K102" s="3">
         <v>-102500</v>

--- a/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELP_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3968500</v>
+        <v>3860500</v>
       </c>
       <c r="E8" s="3">
-        <v>4051400</v>
+        <v>3941100</v>
       </c>
       <c r="F8" s="3">
-        <v>4431300</v>
+        <v>4310700</v>
       </c>
       <c r="G8" s="3">
-        <v>3442700</v>
+        <v>3349000</v>
       </c>
       <c r="H8" s="3">
-        <v>2932000</v>
+        <v>2852200</v>
       </c>
       <c r="I8" s="3">
-        <v>2759300</v>
+        <v>2684200</v>
       </c>
       <c r="J8" s="3">
-        <v>2591200</v>
+        <v>2520600</v>
       </c>
       <c r="K8" s="3">
         <v>2694100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3063600</v>
+        <v>2980200</v>
       </c>
       <c r="E9" s="3">
-        <v>3127700</v>
+        <v>3042500</v>
       </c>
       <c r="F9" s="3">
-        <v>3532500</v>
+        <v>3436400</v>
       </c>
       <c r="G9" s="3">
-        <v>2466100</v>
+        <v>2399000</v>
       </c>
       <c r="H9" s="3">
-        <v>2118100</v>
+        <v>2060500</v>
       </c>
       <c r="I9" s="3">
-        <v>2125100</v>
+        <v>2067200</v>
       </c>
       <c r="J9" s="3">
-        <v>1970600</v>
+        <v>1917000</v>
       </c>
       <c r="K9" s="3">
         <v>2104400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>905000</v>
+        <v>880300</v>
       </c>
       <c r="E10" s="3">
-        <v>923700</v>
+        <v>898500</v>
       </c>
       <c r="F10" s="3">
-        <v>898800</v>
+        <v>874300</v>
       </c>
       <c r="G10" s="3">
-        <v>976500</v>
+        <v>949900</v>
       </c>
       <c r="H10" s="3">
-        <v>813900</v>
+        <v>791700</v>
       </c>
       <c r="I10" s="3">
-        <v>634300</v>
+        <v>617000</v>
       </c>
       <c r="J10" s="3">
-        <v>620600</v>
+        <v>603700</v>
       </c>
       <c r="K10" s="3">
         <v>589700</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>336600</v>
+        <v>327500</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>19100</v>
+        <v>18600</v>
       </c>
       <c r="E15" s="3">
-        <v>15300</v>
+        <v>14900</v>
       </c>
       <c r="F15" s="3">
-        <v>12200</v>
+        <v>11900</v>
       </c>
       <c r="G15" s="3">
-        <v>11900</v>
+        <v>11600</v>
       </c>
       <c r="H15" s="3">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="I15" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="J15" s="3">
-        <v>8400</v>
+        <v>8200</v>
       </c>
       <c r="K15" s="3">
         <v>9000</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3285900</v>
+        <v>3196500</v>
       </c>
       <c r="E17" s="3">
-        <v>3699400</v>
+        <v>3598700</v>
       </c>
       <c r="F17" s="3">
-        <v>3425100</v>
+        <v>3331900</v>
       </c>
       <c r="G17" s="3">
-        <v>2656800</v>
+        <v>2584500</v>
       </c>
       <c r="H17" s="3">
-        <v>2321900</v>
+        <v>2258700</v>
       </c>
       <c r="I17" s="3">
-        <v>2317000</v>
+        <v>2253900</v>
       </c>
       <c r="J17" s="3">
-        <v>2194500</v>
+        <v>2134700</v>
       </c>
       <c r="K17" s="3">
         <v>2273800</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>682600</v>
+        <v>664100</v>
       </c>
       <c r="E18" s="3">
-        <v>351900</v>
+        <v>342400</v>
       </c>
       <c r="F18" s="3">
-        <v>1006200</v>
+        <v>978800</v>
       </c>
       <c r="G18" s="3">
-        <v>785800</v>
+        <v>764400</v>
       </c>
       <c r="H18" s="3">
-        <v>610100</v>
+        <v>593500</v>
       </c>
       <c r="I18" s="3">
-        <v>442300</v>
+        <v>430300</v>
       </c>
       <c r="J18" s="3">
-        <v>396700</v>
+        <v>385900</v>
       </c>
       <c r="K18" s="3">
         <v>420300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>107900</v>
+        <v>105000</v>
       </c>
       <c r="E20" s="3">
-        <v>96900</v>
+        <v>94200</v>
       </c>
       <c r="F20" s="3">
-        <v>97600</v>
+        <v>95000</v>
       </c>
       <c r="G20" s="3">
-        <v>272300</v>
+        <v>264900</v>
       </c>
       <c r="H20" s="3">
-        <v>241200</v>
+        <v>234600</v>
       </c>
       <c r="I20" s="3">
-        <v>80100</v>
+        <v>77900</v>
       </c>
       <c r="J20" s="3">
-        <v>44300</v>
+        <v>43100</v>
       </c>
       <c r="K20" s="3">
         <v>69500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1048100</v>
+        <v>1014600</v>
       </c>
       <c r="E21" s="3">
-        <v>691300</v>
+        <v>667800</v>
       </c>
       <c r="F21" s="3">
-        <v>1305600</v>
+        <v>1266200</v>
       </c>
       <c r="G21" s="3">
-        <v>1246300</v>
+        <v>1208800</v>
       </c>
       <c r="H21" s="3">
-        <v>1055200</v>
+        <v>1022500</v>
       </c>
       <c r="I21" s="3">
-        <v>662000</v>
+        <v>641300</v>
       </c>
       <c r="J21" s="3">
-        <v>577300</v>
+        <v>559000</v>
       </c>
       <c r="K21" s="3">
         <v>635600</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>330500</v>
+        <v>321500</v>
       </c>
       <c r="E22" s="3">
-        <v>273300</v>
+        <v>265800</v>
       </c>
       <c r="F22" s="3">
-        <v>158100</v>
+        <v>153800</v>
       </c>
       <c r="G22" s="3">
-        <v>112300</v>
+        <v>109200</v>
       </c>
       <c r="H22" s="3">
-        <v>325300</v>
+        <v>316500</v>
       </c>
       <c r="I22" s="3">
-        <v>161000</v>
+        <v>156600</v>
       </c>
       <c r="J22" s="3">
-        <v>183600</v>
+        <v>178600</v>
       </c>
       <c r="K22" s="3">
         <v>220600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>460000</v>
+        <v>447500</v>
       </c>
       <c r="E23" s="3">
-        <v>175600</v>
+        <v>170800</v>
       </c>
       <c r="F23" s="3">
-        <v>945700</v>
+        <v>920000</v>
       </c>
       <c r="G23" s="3">
-        <v>945900</v>
+        <v>920100</v>
       </c>
       <c r="H23" s="3">
-        <v>526000</v>
+        <v>511700</v>
       </c>
       <c r="I23" s="3">
-        <v>361400</v>
+        <v>351600</v>
       </c>
       <c r="J23" s="3">
-        <v>257400</v>
+        <v>250400</v>
       </c>
       <c r="K23" s="3">
         <v>269300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>65400</v>
+        <v>63600</v>
       </c>
       <c r="E24" s="3">
-        <v>-36800</v>
+        <v>-35800</v>
       </c>
       <c r="F24" s="3">
-        <v>232700</v>
+        <v>226400</v>
       </c>
       <c r="G24" s="3">
-        <v>237500</v>
+        <v>231000</v>
       </c>
       <c r="H24" s="3">
-        <v>124800</v>
+        <v>121400</v>
       </c>
       <c r="I24" s="3">
-        <v>94600</v>
+        <v>92000</v>
       </c>
       <c r="J24" s="3">
-        <v>50800</v>
+        <v>49400</v>
       </c>
       <c r="K24" s="3">
         <v>106900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>394600</v>
+        <v>383800</v>
       </c>
       <c r="E26" s="3">
-        <v>212300</v>
+        <v>206600</v>
       </c>
       <c r="F26" s="3">
-        <v>713000</v>
+        <v>693600</v>
       </c>
       <c r="G26" s="3">
-        <v>708400</v>
+        <v>689100</v>
       </c>
       <c r="H26" s="3">
-        <v>401200</v>
+        <v>390200</v>
       </c>
       <c r="I26" s="3">
-        <v>266800</v>
+        <v>259500</v>
       </c>
       <c r="J26" s="3">
-        <v>206600</v>
+        <v>201000</v>
       </c>
       <c r="K26" s="3">
         <v>162400</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>382000</v>
+        <v>371600</v>
       </c>
       <c r="E27" s="3">
-        <v>205500</v>
+        <v>199900</v>
       </c>
       <c r="F27" s="3">
-        <v>695300</v>
+        <v>676300</v>
       </c>
       <c r="G27" s="3">
-        <v>707400</v>
+        <v>688100</v>
       </c>
       <c r="H27" s="3">
-        <v>387700</v>
+        <v>377100</v>
       </c>
       <c r="I27" s="3">
-        <v>260000</v>
+        <v>252900</v>
       </c>
       <c r="J27" s="3">
-        <v>191000</v>
+        <v>185800</v>
       </c>
       <c r="K27" s="3">
         <v>170300</v>
@@ -1590,19 +1590,19 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>35400</v>
+        <v>34400</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>219800</v>
+        <v>213800</v>
       </c>
       <c r="G29" s="3">
-        <v>14000</v>
+        <v>13600</v>
       </c>
       <c r="H29" s="3">
-        <v>-20000</v>
+        <v>-19500</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-107900</v>
+        <v>-105000</v>
       </c>
       <c r="E32" s="3">
-        <v>-96900</v>
+        <v>-94200</v>
       </c>
       <c r="F32" s="3">
-        <v>-97600</v>
+        <v>-95000</v>
       </c>
       <c r="G32" s="3">
-        <v>-272300</v>
+        <v>-264900</v>
       </c>
       <c r="H32" s="3">
-        <v>-241200</v>
+        <v>-234600</v>
       </c>
       <c r="I32" s="3">
-        <v>-80100</v>
+        <v>-77900</v>
       </c>
       <c r="J32" s="3">
-        <v>-44300</v>
+        <v>-43100</v>
       </c>
       <c r="K32" s="3">
         <v>-69500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>417300</v>
+        <v>406000</v>
       </c>
       <c r="E33" s="3">
-        <v>205500</v>
+        <v>199900</v>
       </c>
       <c r="F33" s="3">
-        <v>915000</v>
+        <v>890100</v>
       </c>
       <c r="G33" s="3">
-        <v>721300</v>
+        <v>701700</v>
       </c>
       <c r="H33" s="3">
-        <v>367700</v>
+        <v>357700</v>
       </c>
       <c r="I33" s="3">
-        <v>260000</v>
+        <v>252900</v>
       </c>
       <c r="J33" s="3">
-        <v>191000</v>
+        <v>185800</v>
       </c>
       <c r="K33" s="3">
         <v>170300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>417300</v>
+        <v>406000</v>
       </c>
       <c r="E35" s="3">
-        <v>205500</v>
+        <v>199900</v>
       </c>
       <c r="F35" s="3">
-        <v>915000</v>
+        <v>890100</v>
       </c>
       <c r="G35" s="3">
-        <v>721300</v>
+        <v>701700</v>
       </c>
       <c r="H35" s="3">
-        <v>367700</v>
+        <v>357700</v>
       </c>
       <c r="I35" s="3">
-        <v>260000</v>
+        <v>252900</v>
       </c>
       <c r="J35" s="3">
-        <v>191000</v>
+        <v>185800</v>
       </c>
       <c r="K35" s="3">
         <v>170300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1041100</v>
+        <v>1012700</v>
       </c>
       <c r="E41" s="3">
-        <v>494900</v>
+        <v>481400</v>
       </c>
       <c r="F41" s="3">
-        <v>641600</v>
+        <v>624200</v>
       </c>
       <c r="G41" s="3">
-        <v>595400</v>
+        <v>579200</v>
       </c>
       <c r="H41" s="3">
-        <v>543500</v>
+        <v>528700</v>
       </c>
       <c r="I41" s="3">
-        <v>360000</v>
+        <v>350200</v>
       </c>
       <c r="J41" s="3">
-        <v>192200</v>
+        <v>186900</v>
       </c>
       <c r="K41" s="3">
         <v>201900</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="E42" s="3">
-        <v>35300</v>
+        <v>34300</v>
       </c>
       <c r="F42" s="3">
-        <v>73900</v>
+        <v>71900</v>
       </c>
       <c r="G42" s="3">
-        <v>32300</v>
+        <v>31400</v>
       </c>
       <c r="H42" s="3">
-        <v>66300</v>
+        <v>64500</v>
       </c>
       <c r="I42" s="3">
-        <v>100900</v>
+        <v>98100</v>
       </c>
       <c r="J42" s="3">
-        <v>32000</v>
+        <v>31100</v>
       </c>
       <c r="K42" s="3">
         <v>28100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1175100</v>
+        <v>1143100</v>
       </c>
       <c r="E43" s="3">
-        <v>1146100</v>
+        <v>1114900</v>
       </c>
       <c r="F43" s="3">
-        <v>1305400</v>
+        <v>1269900</v>
       </c>
       <c r="G43" s="3">
-        <v>1215600</v>
+        <v>1182500</v>
       </c>
       <c r="H43" s="3">
-        <v>821200</v>
+        <v>798800</v>
       </c>
       <c r="I43" s="3">
-        <v>732200</v>
+        <v>712300</v>
       </c>
       <c r="J43" s="3">
-        <v>776900</v>
+        <v>755700</v>
       </c>
       <c r="K43" s="3">
         <v>658200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>32300</v>
+        <v>31400</v>
       </c>
       <c r="E44" s="3">
-        <v>36000</v>
+        <v>35000</v>
       </c>
       <c r="F44" s="3">
-        <v>36500</v>
+        <v>35500</v>
       </c>
       <c r="G44" s="3">
-        <v>30100</v>
+        <v>29300</v>
       </c>
       <c r="H44" s="3">
-        <v>24100</v>
+        <v>23400</v>
       </c>
       <c r="I44" s="3">
-        <v>21500</v>
+        <v>20900</v>
       </c>
       <c r="J44" s="3">
-        <v>20400</v>
+        <v>19900</v>
       </c>
       <c r="K44" s="3">
         <v>26900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>281900</v>
+        <v>274200</v>
       </c>
       <c r="E45" s="3">
-        <v>11100</v>
+        <v>10800</v>
       </c>
       <c r="F45" s="3">
-        <v>9900</v>
+        <v>9700</v>
       </c>
       <c r="G45" s="3">
-        <v>234200</v>
+        <v>227800</v>
       </c>
       <c r="H45" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="I45" s="3">
-        <v>19200</v>
+        <v>18700</v>
       </c>
       <c r="J45" s="3">
-        <v>32000</v>
+        <v>31200</v>
       </c>
       <c r="K45" s="3">
         <v>19300</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2534100</v>
+        <v>2465100</v>
       </c>
       <c r="E46" s="3">
-        <v>1723300</v>
+        <v>1676400</v>
       </c>
       <c r="F46" s="3">
-        <v>2067400</v>
+        <v>2011200</v>
       </c>
       <c r="G46" s="3">
-        <v>2107600</v>
+        <v>2050300</v>
       </c>
       <c r="H46" s="3">
-        <v>1461300</v>
+        <v>1421500</v>
       </c>
       <c r="I46" s="3">
-        <v>1233800</v>
+        <v>1200200</v>
       </c>
       <c r="J46" s="3">
-        <v>1053500</v>
+        <v>1024800</v>
       </c>
       <c r="K46" s="3">
         <v>871300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3226400</v>
+        <v>3138500</v>
       </c>
       <c r="E47" s="3">
-        <v>3231600</v>
+        <v>3143600</v>
       </c>
       <c r="F47" s="3">
-        <v>3157100</v>
+        <v>3071200</v>
       </c>
       <c r="G47" s="3">
-        <v>2938200</v>
+        <v>2858200</v>
       </c>
       <c r="H47" s="3">
-        <v>1965600</v>
+        <v>1912100</v>
       </c>
       <c r="I47" s="3">
-        <v>1755000</v>
+        <v>1707200</v>
       </c>
       <c r="J47" s="3">
-        <v>1571300</v>
+        <v>1528500</v>
       </c>
       <c r="K47" s="3">
         <v>1559100</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2046900</v>
+        <v>1991100</v>
       </c>
       <c r="E48" s="3">
-        <v>1908800</v>
+        <v>1856900</v>
       </c>
       <c r="F48" s="3">
-        <v>1911700</v>
+        <v>1859700</v>
       </c>
       <c r="G48" s="3">
-        <v>1779000</v>
+        <v>1730600</v>
       </c>
       <c r="H48" s="3">
-        <v>1974300</v>
+        <v>1920500</v>
       </c>
       <c r="I48" s="3">
-        <v>2003200</v>
+        <v>1948600</v>
       </c>
       <c r="J48" s="3">
-        <v>1816300</v>
+        <v>1766900</v>
       </c>
       <c r="K48" s="3">
         <v>1837400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2063800</v>
+        <v>2007600</v>
       </c>
       <c r="E49" s="3">
-        <v>1898900</v>
+        <v>1847200</v>
       </c>
       <c r="F49" s="3">
-        <v>1702700</v>
+        <v>1656300</v>
       </c>
       <c r="G49" s="3">
-        <v>1280300</v>
+        <v>1245400</v>
       </c>
       <c r="H49" s="3">
-        <v>1170000</v>
+        <v>1138200</v>
       </c>
       <c r="I49" s="3">
-        <v>1113900</v>
+        <v>1083600</v>
       </c>
       <c r="J49" s="3">
-        <v>1192200</v>
+        <v>1159800</v>
       </c>
       <c r="K49" s="3">
         <v>1328300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>442000</v>
+        <v>430000</v>
       </c>
       <c r="E52" s="3">
-        <v>420700</v>
+        <v>409200</v>
       </c>
       <c r="F52" s="3">
-        <v>313600</v>
+        <v>305000</v>
       </c>
       <c r="G52" s="3">
-        <v>538800</v>
+        <v>524100</v>
       </c>
       <c r="H52" s="3">
-        <v>507400</v>
+        <v>493600</v>
       </c>
       <c r="I52" s="3">
-        <v>532500</v>
+        <v>518000</v>
       </c>
       <c r="J52" s="3">
-        <v>542400</v>
+        <v>527600</v>
       </c>
       <c r="K52" s="3">
         <v>636100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10313100</v>
+        <v>10032400</v>
       </c>
       <c r="E54" s="3">
-        <v>9183300</v>
+        <v>8933200</v>
       </c>
       <c r="F54" s="3">
-        <v>9152600</v>
+        <v>8903400</v>
       </c>
       <c r="G54" s="3">
-        <v>8643900</v>
+        <v>8408600</v>
       </c>
       <c r="H54" s="3">
-        <v>7078600</v>
+        <v>6885900</v>
       </c>
       <c r="I54" s="3">
-        <v>6638400</v>
+        <v>6457700</v>
       </c>
       <c r="J54" s="3">
-        <v>6127100</v>
+        <v>5960300</v>
       </c>
       <c r="K54" s="3">
         <v>6232300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>398100</v>
+        <v>387200</v>
       </c>
       <c r="E57" s="3">
-        <v>386200</v>
+        <v>375600</v>
       </c>
       <c r="F57" s="3">
-        <v>477700</v>
+        <v>464700</v>
       </c>
       <c r="G57" s="3">
-        <v>423300</v>
+        <v>411800</v>
       </c>
       <c r="H57" s="3">
-        <v>311400</v>
+        <v>302900</v>
       </c>
       <c r="I57" s="3">
-        <v>262200</v>
+        <v>255100</v>
       </c>
       <c r="J57" s="3">
-        <v>311100</v>
+        <v>302600</v>
       </c>
       <c r="K57" s="3">
         <v>258200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>360500</v>
+        <v>350700</v>
       </c>
       <c r="E58" s="3">
-        <v>312300</v>
+        <v>303800</v>
       </c>
       <c r="F58" s="3">
-        <v>512100</v>
+        <v>498100</v>
       </c>
       <c r="G58" s="3">
-        <v>487800</v>
+        <v>474500</v>
       </c>
       <c r="H58" s="3">
-        <v>268500</v>
+        <v>261200</v>
       </c>
       <c r="I58" s="3">
-        <v>609300</v>
+        <v>592700</v>
       </c>
       <c r="J58" s="3">
-        <v>446500</v>
+        <v>434400</v>
       </c>
       <c r="K58" s="3">
         <v>535000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>961400</v>
+        <v>935200</v>
       </c>
       <c r="E59" s="3">
-        <v>623800</v>
+        <v>606900</v>
       </c>
       <c r="F59" s="3">
-        <v>484600</v>
+        <v>471400</v>
       </c>
       <c r="G59" s="3">
-        <v>872600</v>
+        <v>848800</v>
       </c>
       <c r="H59" s="3">
-        <v>407800</v>
+        <v>396700</v>
       </c>
       <c r="I59" s="3">
-        <v>365400</v>
+        <v>355500</v>
       </c>
       <c r="J59" s="3">
-        <v>371300</v>
+        <v>361200</v>
       </c>
       <c r="K59" s="3">
         <v>369800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1720000</v>
+        <v>1673200</v>
       </c>
       <c r="E60" s="3">
-        <v>1322300</v>
+        <v>1286300</v>
       </c>
       <c r="F60" s="3">
-        <v>1474400</v>
+        <v>1434200</v>
       </c>
       <c r="G60" s="3">
-        <v>1783700</v>
+        <v>1735200</v>
       </c>
       <c r="H60" s="3">
-        <v>987700</v>
+        <v>960800</v>
       </c>
       <c r="I60" s="3">
-        <v>1237000</v>
+        <v>1203300</v>
       </c>
       <c r="J60" s="3">
-        <v>1128900</v>
+        <v>1098100</v>
       </c>
       <c r="K60" s="3">
         <v>1163100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2453900</v>
+        <v>2387100</v>
       </c>
       <c r="E61" s="3">
-        <v>2039400</v>
+        <v>1983800</v>
       </c>
       <c r="F61" s="3">
-        <v>1712200</v>
+        <v>1665600</v>
       </c>
       <c r="G61" s="3">
-        <v>1375400</v>
+        <v>1337900</v>
       </c>
       <c r="H61" s="3">
-        <v>1887400</v>
+        <v>1836000</v>
       </c>
       <c r="I61" s="3">
-        <v>1527500</v>
+        <v>1485900</v>
       </c>
       <c r="J61" s="3">
-        <v>1369800</v>
+        <v>1332500</v>
       </c>
       <c r="K61" s="3">
         <v>1282100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1669600</v>
+        <v>1624100</v>
       </c>
       <c r="E62" s="3">
-        <v>1917400</v>
+        <v>1865200</v>
       </c>
       <c r="F62" s="3">
-        <v>1868800</v>
+        <v>1818000</v>
       </c>
       <c r="G62" s="3">
-        <v>1743300</v>
+        <v>1695900</v>
       </c>
       <c r="H62" s="3">
-        <v>952100</v>
+        <v>926200</v>
       </c>
       <c r="I62" s="3">
-        <v>855700</v>
+        <v>832400</v>
       </c>
       <c r="J62" s="3">
-        <v>762700</v>
+        <v>742000</v>
       </c>
       <c r="K62" s="3">
         <v>703200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5899900</v>
+        <v>5739300</v>
       </c>
       <c r="E66" s="3">
-        <v>5337000</v>
+        <v>5191700</v>
       </c>
       <c r="F66" s="3">
-        <v>5117900</v>
+        <v>4978600</v>
       </c>
       <c r="G66" s="3">
-        <v>4956300</v>
+        <v>4821400</v>
       </c>
       <c r="H66" s="3">
-        <v>3891100</v>
+        <v>3785100</v>
       </c>
       <c r="I66" s="3">
-        <v>3676200</v>
+        <v>3576100</v>
       </c>
       <c r="J66" s="3">
-        <v>3317300</v>
+        <v>3227000</v>
       </c>
       <c r="K66" s="3">
         <v>3202600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1963300</v>
+        <v>1909800</v>
       </c>
       <c r="E72" s="3">
-        <v>1741200</v>
+        <v>1693800</v>
       </c>
       <c r="F72" s="3">
-        <v>1707600</v>
+        <v>1661100</v>
       </c>
       <c r="G72" s="3">
-        <v>1348400</v>
+        <v>1311700</v>
       </c>
       <c r="H72" s="3">
-        <v>1082800</v>
+        <v>1053300</v>
       </c>
       <c r="I72" s="3">
-        <v>1355600</v>
+        <v>1318700</v>
       </c>
       <c r="J72" s="3">
-        <v>1182900</v>
+        <v>1150700</v>
       </c>
       <c r="K72" s="3">
         <v>1197800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4413200</v>
+        <v>4293100</v>
       </c>
       <c r="E76" s="3">
-        <v>3846200</v>
+        <v>3741500</v>
       </c>
       <c r="F76" s="3">
-        <v>4034600</v>
+        <v>3924800</v>
       </c>
       <c r="G76" s="3">
-        <v>3687600</v>
+        <v>3587300</v>
       </c>
       <c r="H76" s="3">
-        <v>3187600</v>
+        <v>3100800</v>
       </c>
       <c r="I76" s="3">
-        <v>2962200</v>
+        <v>2881600</v>
       </c>
       <c r="J76" s="3">
-        <v>2809800</v>
+        <v>2733300</v>
       </c>
       <c r="K76" s="3">
         <v>3029700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>417300</v>
+        <v>406000</v>
       </c>
       <c r="E81" s="3">
-        <v>205500</v>
+        <v>199900</v>
       </c>
       <c r="F81" s="3">
-        <v>915000</v>
+        <v>890100</v>
       </c>
       <c r="G81" s="3">
-        <v>721300</v>
+        <v>701700</v>
       </c>
       <c r="H81" s="3">
-        <v>367700</v>
+        <v>357700</v>
       </c>
       <c r="I81" s="3">
-        <v>260000</v>
+        <v>252900</v>
       </c>
       <c r="J81" s="3">
-        <v>191000</v>
+        <v>185800</v>
       </c>
       <c r="K81" s="3">
         <v>170300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>255300</v>
+        <v>248400</v>
       </c>
       <c r="E83" s="3">
-        <v>240400</v>
+        <v>233800</v>
       </c>
       <c r="F83" s="3">
-        <v>200000</v>
+        <v>194600</v>
       </c>
       <c r="G83" s="3">
-        <v>186600</v>
+        <v>181500</v>
       </c>
       <c r="H83" s="3">
-        <v>202100</v>
+        <v>196600</v>
       </c>
       <c r="I83" s="3">
-        <v>138400</v>
+        <v>134600</v>
       </c>
       <c r="J83" s="3">
-        <v>135200</v>
+        <v>131500</v>
       </c>
       <c r="K83" s="3">
         <v>145600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>650100</v>
+        <v>632400</v>
       </c>
       <c r="E89" s="3">
-        <v>721100</v>
+        <v>701400</v>
       </c>
       <c r="F89" s="3">
-        <v>625800</v>
+        <v>608700</v>
       </c>
       <c r="G89" s="3">
-        <v>728100</v>
+        <v>708300</v>
       </c>
       <c r="H89" s="3">
-        <v>544100</v>
+        <v>529300</v>
       </c>
       <c r="I89" s="3">
-        <v>327200</v>
+        <v>318300</v>
       </c>
       <c r="J89" s="3">
-        <v>182800</v>
+        <v>177800</v>
       </c>
       <c r="K89" s="3">
         <v>303700</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-37800</v>
+        <v>-36800</v>
       </c>
       <c r="E91" s="3">
-        <v>-98900</v>
+        <v>-96300</v>
       </c>
       <c r="F91" s="3">
-        <v>-62500</v>
+        <v>-60800</v>
       </c>
       <c r="G91" s="3">
-        <v>-41800</v>
+        <v>-40700</v>
       </c>
       <c r="H91" s="3">
-        <v>-100300</v>
+        <v>-97600</v>
       </c>
       <c r="I91" s="3">
-        <v>-275100</v>
+        <v>-267600</v>
       </c>
       <c r="J91" s="3">
-        <v>-222700</v>
+        <v>-216700</v>
       </c>
       <c r="K91" s="3">
         <v>-264100</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-579200</v>
+        <v>-563500</v>
       </c>
       <c r="E94" s="3">
-        <v>-512700</v>
+        <v>-498800</v>
       </c>
       <c r="F94" s="3">
-        <v>5900</v>
+        <v>5700</v>
       </c>
       <c r="G94" s="3">
-        <v>-308100</v>
+        <v>-299700</v>
       </c>
       <c r="H94" s="3">
-        <v>-307400</v>
+        <v>-299000</v>
       </c>
       <c r="I94" s="3">
-        <v>-397100</v>
+        <v>-386300</v>
       </c>
       <c r="J94" s="3">
-        <v>-292100</v>
+        <v>-284200</v>
       </c>
       <c r="K94" s="3">
         <v>-516400</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-138600</v>
+        <v>-134900</v>
       </c>
       <c r="E96" s="3">
-        <v>-400500</v>
+        <v>-389600</v>
       </c>
       <c r="F96" s="3">
-        <v>-715800</v>
+        <v>-696300</v>
       </c>
       <c r="G96" s="3">
-        <v>-115700</v>
+        <v>-112600</v>
       </c>
       <c r="H96" s="3">
-        <v>-70300</v>
+        <v>-68400</v>
       </c>
       <c r="I96" s="3">
-        <v>-55600</v>
+        <v>-54000</v>
       </c>
       <c r="J96" s="3">
-        <v>-93600</v>
+        <v>-91000</v>
       </c>
       <c r="K96" s="3">
         <v>-75900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>498200</v>
+        <v>484700</v>
       </c>
       <c r="E100" s="3">
-        <v>-355100</v>
+        <v>-345400</v>
       </c>
       <c r="F100" s="3">
-        <v>-532900</v>
+        <v>-518400</v>
       </c>
       <c r="G100" s="3">
-        <v>-316900</v>
+        <v>-308300</v>
       </c>
       <c r="H100" s="3">
-        <v>-53200</v>
+        <v>-51800</v>
       </c>
       <c r="I100" s="3">
-        <v>237700</v>
+        <v>231200</v>
       </c>
       <c r="J100" s="3">
-        <v>120100</v>
+        <v>116800</v>
       </c>
       <c r="K100" s="3">
         <v>110100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>569100</v>
+        <v>553600</v>
       </c>
       <c r="E102" s="3">
-        <v>-146800</v>
+        <v>-142800</v>
       </c>
       <c r="F102" s="3">
-        <v>98700</v>
+        <v>96000</v>
       </c>
       <c r="G102" s="3">
-        <v>103100</v>
+        <v>100300</v>
       </c>
       <c r="H102" s="3">
-        <v>183500</v>
+        <v>178500</v>
       </c>
       <c r="I102" s="3">
-        <v>167800</v>
+        <v>163300</v>
       </c>
       <c r="J102" s="3">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="K102" s="3">
         <v>-102500</v>
